--- a/Data/EventData/SCE_2021.xlsx
+++ b/Data/EventData/SCE_2021.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\starkma\Documents\M&amp;I\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dread\Downloads\Wildfire-Point-Process\Data\EventData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE45D448-E0E6-4DF6-9682-2E3BA13E9853}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34A7FFB-FC26-4456-B200-58087CF835CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="2955" windowWidth="29040" windowHeight="16440" xr2:uid="{BD3B2349-B642-438F-89D4-EB7FD184DA6D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD3B2349-B642-438F-89D4-EB7FD184DA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="2021 Reportables" sheetId="2" r:id="rId1"/>
@@ -345,7 +345,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2636" uniqueCount="318">
   <si>
     <t>Outside Force</t>
   </si>
@@ -527,12 +527,6 @@
     <t>Visalia Fire Department</t>
   </si>
   <si>
-    <t>-119.351557</t>
-  </si>
-  <si>
-    <t>36.329183</t>
-  </si>
-  <si>
     <t>OH-4677220E</t>
   </si>
   <si>
@@ -575,12 +569,6 @@
     <t>OH-1072790E</t>
   </si>
   <si>
-    <t>-117.956725</t>
-  </si>
-  <si>
-    <t>34.034592</t>
-  </si>
-  <si>
     <t>UG-5351883</t>
   </si>
   <si>
@@ -606,12 +594,6 @@
   </si>
   <si>
     <t>Rancho Cucamonga Fire Department</t>
-  </si>
-  <si>
-    <t>-117.564728</t>
-  </si>
-  <si>
-    <t>34.162183</t>
   </si>
   <si>
     <t>OH-2177032E</t>
@@ -1323,7 +1305,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
@@ -1844,6 +1826,12 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1880,12 +1868,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1893,70 +1875,7 @@
     <cellStyle name="Normal 4" xfId="2" xr:uid="{E5E82BBC-A907-4CED-A4DF-30ED5A31C5C1}"/>
     <cellStyle name="Normal_Sheet1" xfId="3" xr:uid="{56BD7D50-FC1C-428A-824D-7229A0485B36}"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -1989,41 +1908,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color auto="1"/>
       </font>
@@ -2047,63 +1931,10 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2E3125D1-EB5E-42EE-85B8-290DED459799}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2116,7 +1947,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="CPUC Sample Interactive"/>
@@ -2395,9 +2226,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2435,7 +2266,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2541,7 +2372,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2683,7 +2514,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2692,141 +2523,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090D82BB-7471-40DB-BECD-CE894B1F314E}">
   <dimension ref="A1:W175"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16.1796875" customWidth="1"/>
-    <col min="10" max="10" width="33.54296875" customWidth="1"/>
-    <col min="11" max="11" width="23.36328125" customWidth="1"/>
-    <col min="12" max="12" width="26.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" customWidth="1"/>
+    <col min="10" max="10" width="33.5546875" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" customWidth="1"/>
+    <col min="12" max="12" width="26.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.109375" customWidth="1"/>
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7265625" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.77734375" customWidth="1"/>
+    <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.1796875" customWidth="1"/>
+    <col min="23" max="23" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A1" s="87" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="85" t="s">
-        <v>318</v>
-      </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="89" t="s">
-        <v>319</v>
-      </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="91" t="s">
-        <v>320</v>
-      </c>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93" t="s">
-        <v>321</v>
-      </c>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="95" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="97" t="s">
-        <v>323</v>
-      </c>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-    </row>
-    <row r="2" spans="1:23" ht="39" x14ac:dyDescent="0.35">
-      <c r="A2" s="88"/>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="s">
+        <v>304</v>
+      </c>
+      <c r="B1" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="91" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="93" t="s">
+        <v>314</v>
+      </c>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95" t="s">
+        <v>315</v>
+      </c>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="97" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="85" t="s">
+        <v>317</v>
+      </c>
+      <c r="T1" s="86"/>
+      <c r="U1" s="86"/>
+      <c r="V1" s="86"/>
+      <c r="W1" s="86"/>
+    </row>
+    <row r="2" spans="1:23" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="90"/>
       <c r="B2" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>289</v>
+      </c>
+      <c r="D2" s="82" t="s">
+        <v>303</v>
+      </c>
+      <c r="E2" s="81" t="s">
+        <v>302</v>
+      </c>
+      <c r="F2" s="80" t="s">
+        <v>301</v>
+      </c>
+      <c r="G2" s="80" t="s">
+        <v>300</v>
+      </c>
+      <c r="H2" s="79" t="s">
+        <v>299</v>
+      </c>
+      <c r="I2" s="79" t="s">
+        <v>298</v>
+      </c>
+      <c r="J2" s="79" t="s">
+        <v>297</v>
+      </c>
+      <c r="K2" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="L2" s="78" t="s">
         <v>295</v>
       </c>
-      <c r="D2" s="82" t="s">
-        <v>309</v>
-      </c>
-      <c r="E2" s="81" t="s">
-        <v>308</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>307</v>
-      </c>
-      <c r="G2" s="80" t="s">
-        <v>306</v>
-      </c>
-      <c r="H2" s="79" t="s">
-        <v>305</v>
-      </c>
-      <c r="I2" s="79" t="s">
-        <v>304</v>
-      </c>
-      <c r="J2" s="79" t="s">
-        <v>303</v>
-      </c>
-      <c r="K2" s="78" t="s">
-        <v>302</v>
-      </c>
-      <c r="L2" s="78" t="s">
-        <v>301</v>
-      </c>
       <c r="M2" s="78" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N2" s="78" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="O2" s="78" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P2" s="77" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q2" s="77" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="R2" s="77" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="S2" s="76" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="T2" s="76" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="U2" s="76" t="s">
         <v>3</v>
       </c>
       <c r="V2" s="76" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="W2" s="76" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>14</v>
       </c>
@@ -2855,16 +2686,16 @@
         <v>10</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>6</v>
@@ -2893,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>14</v>
       </c>
@@ -2923,13 +2754,13 @@
       </c>
       <c r="J4" s="17"/>
       <c r="K4" s="8" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>24</v>
@@ -2960,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>14</v>
       </c>
@@ -2989,16 +2820,16 @@
         <v>10</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>24</v>
@@ -3025,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="51" t="s">
         <v>14</v>
       </c>
@@ -3054,16 +2885,16 @@
         <v>10</v>
       </c>
       <c r="J6" s="65" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="L6" s="74" t="s">
         <v>16</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N6" s="64" t="s">
         <v>24</v>
@@ -3086,7 +2917,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="51" t="s">
         <v>14</v>
       </c>
@@ -3115,16 +2946,16 @@
         <v>10</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>24</v>
@@ -3155,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="51" t="s">
         <v>14</v>
       </c>
@@ -3185,13 +3016,13 @@
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>6</v>
@@ -3216,7 +3047,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="51" t="s">
         <v>14</v>
       </c>
@@ -3248,13 +3079,13 @@
         <v>29</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>24</v>
@@ -3283,7 +3114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="51" t="s">
         <v>14</v>
       </c>
@@ -3313,13 +3144,13 @@
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="8" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>6</v>
@@ -3342,7 +3173,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="51" t="s">
         <v>14</v>
       </c>
@@ -3371,16 +3202,16 @@
         <v>10</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>15</v>
@@ -3405,7 +3236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
         <v>14</v>
       </c>
@@ -3434,16 +3265,16 @@
         <v>10</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>24</v>
@@ -3457,7 +3288,7 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="4"/>
       <c r="S12" s="44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T12" s="59"/>
       <c r="U12" s="1"/>
@@ -3466,7 +3297,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="51" t="s">
         <v>14</v>
       </c>
@@ -3498,13 +3329,13 @@
         <v>29</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>6</v>
@@ -3531,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="51" t="s">
         <v>14</v>
       </c>
@@ -3561,13 +3392,13 @@
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>6</v>
@@ -3598,7 +3429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="51" t="s">
         <v>14</v>
       </c>
@@ -3627,16 +3458,16 @@
         <v>10</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>24</v>
@@ -3667,7 +3498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="51" t="s">
         <v>14</v>
       </c>
@@ -3693,20 +3524,20 @@
         <v>11</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="8" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>5</v>
@@ -3724,7 +3555,7 @@
         <v>26</v>
       </c>
       <c r="T16" s="54" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -3732,7 +3563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="51" t="s">
         <v>14</v>
       </c>
@@ -3762,13 +3593,13 @@
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>6</v>
@@ -3790,7 +3621,7 @@
       </c>
       <c r="T17" s="59"/>
       <c r="U17" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V17" s="1" t="s">
         <v>1</v>
@@ -3799,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="51" t="s">
         <v>14</v>
       </c>
@@ -3828,16 +3659,16 @@
         <v>10</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>6</v>
@@ -3866,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="51" t="s">
         <v>14</v>
       </c>
@@ -3896,13 +3727,13 @@
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>24</v>
@@ -3933,7 +3764,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="51" t="s">
         <v>14</v>
       </c>
@@ -3962,16 +3793,16 @@
         <v>10</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N20" s="7" t="s">
         <v>6</v>
@@ -4002,7 +3833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="51" t="s">
         <v>14</v>
       </c>
@@ -4032,13 +3863,13 @@
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="8" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>24</v>
@@ -4061,7 +3892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="51" t="s">
         <v>14</v>
       </c>
@@ -4090,16 +3921,16 @@
         <v>10</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>6</v>
@@ -4126,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="51" t="s">
         <v>14</v>
       </c>
@@ -4155,19 +3986,19 @@
         <v>10</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>5</v>
@@ -4191,7 +4022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="51" t="s">
         <v>14</v>
       </c>
@@ -4220,16 +4051,16 @@
         <v>10</v>
       </c>
       <c r="J24" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>253</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>259</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N24" s="7" t="s">
         <v>6</v>
@@ -4256,7 +4087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="51" t="s">
         <v>14</v>
       </c>
@@ -4286,13 +4117,13 @@
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>6</v>
@@ -4321,7 +4152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="51" t="s">
         <v>14</v>
       </c>
@@ -4351,13 +4182,13 @@
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="8" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N26" s="7" t="s">
         <v>56</v>
@@ -4388,7 +4219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
         <v>14</v>
       </c>
@@ -4418,13 +4249,13 @@
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>6</v>
@@ -4449,7 +4280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="51" t="s">
         <v>14</v>
       </c>
@@ -4459,11 +4290,11 @@
       <c r="C28" s="14">
         <v>0.47152777777777777</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>178</v>
+      <c r="D28" s="13">
+        <v>34.559443999999999</v>
+      </c>
+      <c r="E28" s="12">
+        <v>-117.956667</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>24</v>
@@ -4479,13 +4310,13 @@
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="8" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N28" s="7" t="s">
         <v>6</v>
@@ -4512,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="51" t="s">
         <v>14</v>
       </c>
@@ -4544,13 +4375,13 @@
         <v>49</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>6</v>
@@ -4575,7 +4406,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="51" t="s">
         <v>14</v>
       </c>
@@ -4605,13 +4436,13 @@
       </c>
       <c r="J30" s="17"/>
       <c r="K30" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N30" s="7" t="s">
         <v>24</v>
@@ -4640,7 +4471,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="51" t="s">
         <v>14</v>
       </c>
@@ -4669,16 +4500,16 @@
         <v>10</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N31" s="7" t="s">
         <v>6</v>
@@ -4709,7 +4540,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="51" t="s">
         <v>14</v>
       </c>
@@ -4738,16 +4569,16 @@
         <v>10</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N32" s="7" t="s">
         <v>24</v>
@@ -4776,7 +4607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="51" t="s">
         <v>14</v>
       </c>
@@ -4805,16 +4636,16 @@
         <v>10</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N33" s="7" t="s">
         <v>56</v>
@@ -4841,7 +4672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" s="51" t="s">
         <v>14</v>
       </c>
@@ -4871,13 +4702,13 @@
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="8" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N34" s="7" t="s">
         <v>15</v>
@@ -4902,7 +4733,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" s="51" t="s">
         <v>14</v>
       </c>
@@ -4931,16 +4762,16 @@
         <v>10</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N35" s="7" t="s">
         <v>24</v>
@@ -4967,7 +4798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="51" t="s">
         <v>14</v>
       </c>
@@ -4996,16 +4827,16 @@
         <v>10</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N36" s="7" t="s">
         <v>24</v>
@@ -5036,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="51" t="s">
         <v>14</v>
       </c>
@@ -5066,13 +4897,13 @@
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="8" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N37" s="7" t="s">
         <v>24</v>
@@ -5101,7 +4932,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" s="51" t="s">
         <v>14</v>
       </c>
@@ -5131,13 +4962,13 @@
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N38" s="7" t="s">
         <v>25</v>
@@ -5166,7 +4997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="51" t="s">
         <v>14</v>
       </c>
@@ -5195,16 +5026,16 @@
         <v>10</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N39" s="7" t="s">
         <v>6</v>
@@ -5233,7 +5064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="51" t="s">
         <v>14</v>
       </c>
@@ -5265,13 +5096,13 @@
         <v>49</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N40" s="7" t="s">
         <v>24</v>
@@ -5302,7 +5133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="51" t="s">
         <v>14</v>
       </c>
@@ -5332,13 +5163,13 @@
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="8" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N41" s="7" t="s">
         <v>6</v>
@@ -5365,7 +5196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="51" t="s">
         <v>14</v>
       </c>
@@ -5394,16 +5225,16 @@
         <v>10</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N42" s="7" t="s">
         <v>6</v>
@@ -5434,7 +5265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="51" t="s">
         <v>14</v>
       </c>
@@ -5464,13 +5295,13 @@
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N43" s="7" t="s">
         <v>24</v>
@@ -5492,7 +5323,7 @@
       </c>
       <c r="T43" s="59"/>
       <c r="U43" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>1</v>
@@ -5501,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="51" t="s">
         <v>14</v>
       </c>
@@ -5530,16 +5361,16 @@
         <v>10</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N44" s="7" t="s">
         <v>6</v>
@@ -5568,7 +5399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="51" t="s">
         <v>14</v>
       </c>
@@ -5597,16 +5428,16 @@
         <v>10</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N45" s="7" t="s">
         <v>6</v>
@@ -5633,7 +5464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="51" t="s">
         <v>14</v>
       </c>
@@ -5665,13 +5496,13 @@
         <v>29</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N46" s="7" t="s">
         <v>6</v>
@@ -5700,7 +5531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="51" t="s">
         <v>14</v>
       </c>
@@ -5729,16 +5560,16 @@
         <v>18</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N47" s="7" t="s">
         <v>6</v>
@@ -5769,7 +5600,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="51" t="s">
         <v>14</v>
       </c>
@@ -5801,13 +5632,13 @@
         <v>59</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N48" s="7" t="s">
         <v>6</v>
@@ -5838,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="51" t="s">
         <v>14</v>
       </c>
@@ -5867,16 +5698,16 @@
         <v>10</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N49" s="7" t="s">
         <v>56</v>
@@ -5901,7 +5732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="51" t="s">
         <v>14</v>
       </c>
@@ -5927,19 +5758,19 @@
         <v>11</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>6</v>
@@ -5966,7 +5797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="51" t="s">
         <v>14</v>
       </c>
@@ -5995,16 +5826,16 @@
         <v>10</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N51" s="7" t="s">
         <v>6</v>
@@ -6033,7 +5864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="51" t="s">
         <v>14</v>
       </c>
@@ -6062,16 +5893,16 @@
         <v>10</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N52" s="7" t="s">
         <v>6</v>
@@ -6102,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="51" t="s">
         <v>14</v>
       </c>
@@ -6131,19 +5962,19 @@
         <v>10</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>5</v>
@@ -6157,7 +5988,7 @@
         <v>26</v>
       </c>
       <c r="T53" s="54" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
@@ -6165,7 +5996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="51" t="s">
         <v>14</v>
       </c>
@@ -6195,13 +6026,13 @@
       </c>
       <c r="J54" s="17"/>
       <c r="K54" s="8" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N54" s="7" t="s">
         <v>6</v>
@@ -6232,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="51" t="s">
         <v>14</v>
       </c>
@@ -6264,13 +6095,13 @@
         <v>49</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N55" s="7" t="s">
         <v>6</v>
@@ -6297,7 +6128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="51" t="s">
         <v>14</v>
       </c>
@@ -6326,16 +6157,16 @@
         <v>10</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N56" s="7" t="s">
         <v>6</v>
@@ -6362,7 +6193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A57" s="51" t="s">
         <v>14</v>
       </c>
@@ -6394,13 +6225,13 @@
         <v>29</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N57" s="7" t="s">
         <v>24</v>
@@ -6427,7 +6258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" s="51" t="s">
         <v>14</v>
       </c>
@@ -6453,17 +6284,17 @@
         <v>11</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="8" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N58" s="7" t="s">
         <v>15</v>
@@ -6494,7 +6325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" s="51" t="s">
         <v>14</v>
       </c>
@@ -6523,16 +6354,16 @@
         <v>10</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N59" s="7" t="s">
         <v>6</v>
@@ -6557,7 +6388,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" s="51" t="s">
         <v>14</v>
       </c>
@@ -6586,16 +6417,16 @@
         <v>10</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N60" s="7" t="s">
         <v>6</v>
@@ -6622,7 +6453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" s="51" t="s">
         <v>14</v>
       </c>
@@ -6651,16 +6482,16 @@
         <v>10</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>6</v>
@@ -6687,7 +6518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" s="51" t="s">
         <v>14</v>
       </c>
@@ -6717,13 +6548,13 @@
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N62" s="7" t="s">
         <v>25</v>
@@ -6752,7 +6583,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" s="51" t="s">
         <v>14</v>
       </c>
@@ -6782,13 +6613,13 @@
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N63" s="7" t="s">
         <v>24</v>
@@ -6815,7 +6646,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" s="51" t="s">
         <v>14</v>
       </c>
@@ -6844,16 +6675,16 @@
         <v>10</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N64" s="7" t="s">
         <v>24</v>
@@ -6882,7 +6713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" s="51" t="s">
         <v>14</v>
       </c>
@@ -6911,16 +6742,16 @@
         <v>10</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N65" s="7" t="s">
         <v>6</v>
@@ -6945,7 +6776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" s="51" t="s">
         <v>14</v>
       </c>
@@ -6974,16 +6805,16 @@
         <v>10</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N66" s="7" t="s">
         <v>56</v>
@@ -7010,7 +6841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67" s="51" t="s">
         <v>14</v>
       </c>
@@ -7039,16 +6870,16 @@
         <v>10</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N67" s="7" t="s">
         <v>24</v>
@@ -7071,7 +6902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" s="51" t="s">
         <v>14</v>
       </c>
@@ -7100,19 +6931,19 @@
         <v>10</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M68" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N68" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="O68" s="7" t="s">
         <v>5</v>
@@ -7140,7 +6971,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" s="51" t="s">
         <v>14</v>
       </c>
@@ -7169,16 +7000,16 @@
         <v>10</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N69" s="7" t="s">
         <v>6</v>
@@ -7209,7 +7040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" s="51" t="s">
         <v>14</v>
       </c>
@@ -7241,13 +7072,13 @@
         <v>29</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N70" s="7" t="s">
         <v>24</v>
@@ -7274,7 +7105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" s="51" t="s">
         <v>14</v>
       </c>
@@ -7304,16 +7135,16 @@
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="9" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O71" s="7" t="s">
         <v>5</v>
@@ -7322,7 +7153,7 @@
         <v>27</v>
       </c>
       <c r="Q71" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="R71" s="4">
         <v>0.43402777777777773</v>
@@ -7341,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" s="51" t="s">
         <v>14</v>
       </c>
@@ -7370,16 +7201,16 @@
         <v>10</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N72" s="7" t="s">
         <v>24</v>
@@ -7406,7 +7237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:23" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A73" s="51" t="s">
         <v>14</v>
       </c>
@@ -7435,16 +7266,16 @@
         <v>10</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N73" s="7" t="s">
         <v>24</v>
@@ -7471,7 +7302,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" s="51" t="s">
         <v>14</v>
       </c>
@@ -7500,16 +7331,16 @@
         <v>10</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M74" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N74" s="7" t="s">
         <v>24</v>
@@ -7534,7 +7365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:23" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A75" s="51" t="s">
         <v>14</v>
       </c>
@@ -7544,11 +7375,11 @@
       <c r="C75" s="14">
         <v>0.84375</v>
       </c>
-      <c r="D75" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="E75" s="52" t="s">
-        <v>178</v>
+      <c r="D75" s="46">
+        <v>34.488540999999998</v>
+      </c>
+      <c r="E75" s="52">
+        <v>-118.616784</v>
       </c>
       <c r="F75" s="11" t="s">
         <v>13</v>
@@ -7560,17 +7391,17 @@
         <v>11</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J75" s="17"/>
       <c r="K75" s="8" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N75" s="7" t="s">
         <v>24</v>
@@ -7593,7 +7424,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" s="51" t="s">
         <v>14</v>
       </c>
@@ -7625,13 +7456,13 @@
         <v>49</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N76" s="7" t="s">
         <v>24</v>
@@ -7660,7 +7491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" s="51" t="s">
         <v>14</v>
       </c>
@@ -7689,16 +7520,16 @@
         <v>10</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N77" s="7" t="s">
         <v>6</v>
@@ -7712,7 +7543,7 @@
       <c r="Q77" s="5"/>
       <c r="R77" s="4"/>
       <c r="S77" s="44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
@@ -7721,7 +7552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" s="51" t="s">
         <v>14</v>
       </c>
@@ -7750,16 +7581,16 @@
         <v>10</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M78" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N78" s="7" t="s">
         <v>24</v>
@@ -7773,7 +7604,7 @@
       <c r="Q78" s="5"/>
       <c r="R78" s="4"/>
       <c r="S78" s="44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T78" s="28"/>
       <c r="U78" s="28"/>
@@ -7782,7 +7613,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" s="51" t="s">
         <v>14</v>
       </c>
@@ -7814,13 +7645,13 @@
         <v>29</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N79" s="7" t="s">
         <v>6</v>
@@ -7845,7 +7676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="51" t="s">
         <v>14</v>
       </c>
@@ -7877,13 +7708,13 @@
         <v>29</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N80" s="7" t="s">
         <v>6</v>
@@ -7912,7 +7743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81" s="51" t="s">
         <v>14</v>
       </c>
@@ -7941,16 +7772,16 @@
         <v>10</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N81" s="7" t="s">
         <v>6</v>
@@ -7979,7 +7810,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82" s="51" t="s">
         <v>14</v>
       </c>
@@ -8009,13 +7840,13 @@
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M82" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N82" s="7" t="s">
         <v>6</v>
@@ -8044,7 +7875,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83" s="51" t="s">
         <v>14</v>
       </c>
@@ -8067,22 +7898,22 @@
         <v>33</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>10</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N83" s="7" t="s">
         <v>24</v>
@@ -8109,7 +7940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="51" t="s">
         <v>14</v>
       </c>
@@ -8141,13 +7972,13 @@
         <v>29</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="L84" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M84" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N84" s="7" t="s">
         <v>15</v>
@@ -8178,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85" s="51" t="s">
         <v>14</v>
       </c>
@@ -8208,13 +8039,13 @@
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N85" s="7" t="s">
         <v>6</v>
@@ -8243,7 +8074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86" s="51" t="s">
         <v>14</v>
       </c>
@@ -8269,19 +8100,19 @@
         <v>11</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M86" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N86" s="7" t="s">
         <v>6</v>
@@ -8310,7 +8141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87" s="51" t="s">
         <v>14</v>
       </c>
@@ -8321,10 +8152,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D87" s="46" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E87" s="52" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>13</v>
@@ -8339,16 +8170,16 @@
         <v>10</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N87" s="7" t="s">
         <v>24</v>
@@ -8375,7 +8206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88" s="51" t="s">
         <v>14</v>
       </c>
@@ -8407,13 +8238,13 @@
         <v>29</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N88" s="7" t="s">
         <v>6</v>
@@ -8444,7 +8275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89" s="51" t="s">
         <v>14</v>
       </c>
@@ -8473,16 +8304,16 @@
         <v>10</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N89" s="7" t="s">
         <v>24</v>
@@ -8509,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" s="20" t="s">
         <v>14</v>
       </c>
@@ -8538,16 +8369,16 @@
         <v>10</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M90" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N90" s="7" t="s">
         <v>24</v>
@@ -8578,7 +8409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" s="20" t="s">
         <v>14</v>
       </c>
@@ -8592,7 +8423,7 @@
         <v>33.705052999999999</v>
       </c>
       <c r="E91" s="49">
-        <v>117.193673</v>
+        <v>-117.193673</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>24</v>
@@ -8608,13 +8439,13 @@
       </c>
       <c r="J91" s="17"/>
       <c r="K91" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N91" s="7" t="s">
         <v>6</v>
@@ -8643,7 +8474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92" s="20" t="s">
         <v>14</v>
       </c>
@@ -8673,13 +8504,13 @@
       </c>
       <c r="J92" s="17"/>
       <c r="K92" s="8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M92" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N92" s="7" t="s">
         <v>56</v>
@@ -8708,7 +8539,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93" s="20" t="s">
         <v>14</v>
       </c>
@@ -8738,13 +8569,13 @@
       </c>
       <c r="J93" s="17"/>
       <c r="K93" s="8" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N93" s="7" t="s">
         <v>6</v>
@@ -8773,7 +8604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94" s="20" t="s">
         <v>14</v>
       </c>
@@ -8802,16 +8633,16 @@
         <v>10</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N94" s="7" t="s">
         <v>6</v>
@@ -8823,7 +8654,7 @@
         <v>4</v>
       </c>
       <c r="Q94" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="R94" s="4"/>
       <c r="S94" s="44" t="s">
@@ -8840,7 +8671,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95" s="20" t="s">
         <v>14</v>
       </c>
@@ -8870,13 +8701,13 @@
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="L95" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N95" s="7" t="s">
         <v>24</v>
@@ -8905,7 +8736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96" s="20" t="s">
         <v>14</v>
       </c>
@@ -8935,13 +8766,13 @@
       </c>
       <c r="J96" s="17"/>
       <c r="K96" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N96" s="7" t="s">
         <v>56</v>
@@ -8970,7 +8801,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" s="20" t="s">
         <v>14</v>
       </c>
@@ -8999,16 +8830,16 @@
         <v>10</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N97" s="7" t="s">
         <v>6</v>
@@ -9039,7 +8870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" s="20" t="s">
         <v>14</v>
       </c>
@@ -9068,16 +8899,16 @@
         <v>10</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N98" s="7" t="s">
         <v>24</v>
@@ -9106,7 +8937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" s="20" t="s">
         <v>14</v>
       </c>
@@ -9132,17 +8963,17 @@
         <v>11</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="8" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N99" s="7" t="s">
         <v>6</v>
@@ -9173,7 +9004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100" s="20" t="s">
         <v>14</v>
       </c>
@@ -9202,16 +9033,16 @@
         <v>10</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N100" s="7" t="s">
         <v>6</v>
@@ -9229,7 +9060,7 @@
       </c>
       <c r="T100" s="28"/>
       <c r="U100" s="29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V100" s="1" t="s">
         <v>1</v>
@@ -9238,7 +9069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" s="20" t="s">
         <v>14</v>
       </c>
@@ -9267,16 +9098,16 @@
         <v>10</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N101" s="7" t="s">
         <v>6</v>
@@ -9303,7 +9134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" s="20" t="s">
         <v>14</v>
       </c>
@@ -9335,13 +9166,13 @@
         <v>29</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N102" s="7" t="s">
         <v>6</v>
@@ -9372,7 +9203,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="20" t="s">
         <v>14</v>
       </c>
@@ -9401,16 +9232,16 @@
         <v>10</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N103" s="7" t="s">
         <v>6</v>
@@ -9441,7 +9272,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" s="20" t="s">
         <v>14</v>
       </c>
@@ -9471,13 +9302,13 @@
       </c>
       <c r="J104" s="17"/>
       <c r="K104" s="8" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="L104" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M104" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N104" s="7" t="s">
         <v>6</v>
@@ -9508,7 +9339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105" s="20" t="s">
         <v>14</v>
       </c>
@@ -9537,16 +9368,16 @@
         <v>10</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N105" s="7" t="s">
         <v>6</v>
@@ -9568,7 +9399,7 @@
       </c>
       <c r="T105" s="28"/>
       <c r="U105" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V105" s="1" t="s">
         <v>1</v>
@@ -9577,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="20" t="s">
         <v>14</v>
       </c>
@@ -9609,13 +9440,13 @@
         <v>41</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N106" s="7" t="s">
         <v>24</v>
@@ -9642,7 +9473,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" s="20" t="s">
         <v>14</v>
       </c>
@@ -9653,10 +9484,10 @@
         <v>0.73819444444444438</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>54</v>
@@ -9672,13 +9503,13 @@
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N107" s="7" t="s">
         <v>24</v>
@@ -9707,7 +9538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108" s="20" t="s">
         <v>14</v>
       </c>
@@ -9736,16 +9567,16 @@
         <v>10</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K108" s="8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M108" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N108" s="7" t="s">
         <v>15</v>
@@ -9772,7 +9603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109" s="20" t="s">
         <v>14</v>
       </c>
@@ -9804,13 +9635,13 @@
         <v>41</v>
       </c>
       <c r="K109" s="8" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N109" s="7" t="s">
         <v>15</v>
@@ -9837,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110" s="20" t="s">
         <v>14</v>
       </c>
@@ -9866,16 +9697,16 @@
         <v>10</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N110" s="7" t="s">
         <v>24</v>
@@ -9897,16 +9728,16 @@
       </c>
       <c r="T110" s="28"/>
       <c r="U110" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V110" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="W110" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="20" t="s">
         <v>14</v>
       </c>
@@ -9936,13 +9767,13 @@
       </c>
       <c r="J111" s="17"/>
       <c r="K111" s="8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N111" s="7" t="s">
         <v>24</v>
@@ -9969,7 +9800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112" s="20" t="s">
         <v>14</v>
       </c>
@@ -9999,13 +9830,13 @@
       </c>
       <c r="J112" s="17"/>
       <c r="K112" s="9" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L112" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N112" s="7" t="s">
         <v>24</v>
@@ -10019,7 +9850,7 @@
       <c r="Q112" s="5"/>
       <c r="R112" s="4"/>
       <c r="S112" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
@@ -10028,7 +9859,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113" s="20" t="s">
         <v>14</v>
       </c>
@@ -10054,17 +9885,17 @@
         <v>11</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="8" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N113" s="7" t="s">
         <v>24</v>
@@ -10089,7 +9920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114" s="20" t="s">
         <v>14</v>
       </c>
@@ -10115,17 +9946,17 @@
         <v>11</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M114" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N114" s="7" t="s">
         <v>6</v>
@@ -10154,7 +9985,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115" s="20" t="s">
         <v>14</v>
       </c>
@@ -10183,16 +10014,16 @@
         <v>10</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K115" s="8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N115" s="7" t="s">
         <v>6</v>
@@ -10217,7 +10048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116" s="20" t="s">
         <v>14</v>
       </c>
@@ -10246,16 +10077,16 @@
         <v>10</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K116" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M116" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N116" s="7" t="s">
         <v>6</v>
@@ -10282,7 +10113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117" s="20" t="s">
         <v>14</v>
       </c>
@@ -10312,13 +10143,13 @@
       </c>
       <c r="J117" s="17"/>
       <c r="K117" s="9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="L117" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N117" s="7" t="s">
         <v>24</v>
@@ -10336,7 +10167,7 @@
       </c>
       <c r="T117" s="3"/>
       <c r="U117" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V117" s="1" t="s">
         <v>1</v>
@@ -10345,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="20" t="s">
         <v>14</v>
       </c>
@@ -10375,13 +10206,13 @@
       </c>
       <c r="J118" s="17"/>
       <c r="K118" s="8" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M118" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N118" s="7" t="s">
         <v>6</v>
@@ -10410,7 +10241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119" s="20" t="s">
         <v>14</v>
       </c>
@@ -10440,13 +10271,13 @@
       </c>
       <c r="J119" s="10"/>
       <c r="K119" s="8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M119" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N119" s="7" t="s">
         <v>6</v>
@@ -10467,7 +10298,7 @@
         <v>26</v>
       </c>
       <c r="T119" s="25" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="U119" s="21"/>
       <c r="V119" s="18"/>
@@ -10475,7 +10306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120" s="20" t="s">
         <v>14</v>
       </c>
@@ -10504,16 +10335,16 @@
         <v>10</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="M120" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N120" s="7" t="s">
         <v>6</v>
@@ -10544,7 +10375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121" s="16" t="s">
         <v>14</v>
       </c>
@@ -10555,10 +10386,10 @@
         <v>0.5131944444444444</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>24</v>
@@ -10576,13 +10407,13 @@
         <v>29</v>
       </c>
       <c r="K121" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M121" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N121" s="7" t="s">
         <v>6</v>
@@ -10604,7 +10435,7 @@
       </c>
       <c r="T121" s="27"/>
       <c r="U121" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V121" s="1" t="s">
         <v>1</v>
@@ -10613,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A122" s="20" t="s">
         <v>14</v>
       </c>
@@ -10639,17 +10470,17 @@
         <v>11</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J122" s="17"/>
       <c r="K122" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M122" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N122" s="7" t="s">
         <v>6</v>
@@ -10678,7 +10509,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A123" s="20" t="s">
         <v>14</v>
       </c>
@@ -10708,13 +10539,13 @@
       </c>
       <c r="J123" s="17"/>
       <c r="K123" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M123" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N123" s="7" t="s">
         <v>24</v>
@@ -10743,7 +10574,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A124" s="20" t="s">
         <v>14</v>
       </c>
@@ -10773,13 +10604,13 @@
       </c>
       <c r="J124" s="17"/>
       <c r="K124" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M124" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N124" s="7" t="s">
         <v>24</v>
@@ -10806,7 +10637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A125" s="20" t="s">
         <v>14</v>
       </c>
@@ -10832,17 +10663,17 @@
         <v>11</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J125" s="17"/>
       <c r="K125" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M125" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N125" s="7" t="s">
         <v>6</v>
@@ -10871,7 +10702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A126" s="20" t="s">
         <v>14</v>
       </c>
@@ -10897,17 +10728,17 @@
         <v>11</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J126" s="17"/>
       <c r="K126" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M126" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N126" s="7" t="s">
         <v>25</v>
@@ -10936,7 +10767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A127" s="20" t="s">
         <v>14</v>
       </c>
@@ -10965,16 +10796,16 @@
         <v>10</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L127" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M127" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N127" s="7" t="s">
         <v>6</v>
@@ -11005,7 +10836,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128" s="20" t="s">
         <v>14</v>
       </c>
@@ -11034,16 +10865,16 @@
         <v>10</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="K128" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M128" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N128" s="7" t="s">
         <v>24</v>
@@ -11072,7 +10903,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A129" s="20" t="s">
         <v>14</v>
       </c>
@@ -11101,16 +10932,16 @@
         <v>10</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="K129" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M129" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N129" s="7" t="s">
         <v>6</v>
@@ -11137,7 +10968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A130" s="20" t="s">
         <v>14</v>
       </c>
@@ -11167,13 +10998,13 @@
       </c>
       <c r="J130" s="17"/>
       <c r="K130" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M130" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N130" s="7" t="s">
         <v>56</v>
@@ -11202,7 +11033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131" s="16" t="s">
         <v>14</v>
       </c>
@@ -11213,10 +11044,10 @@
         <v>0.69513888888888886</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>24</v>
@@ -11225,20 +11056,20 @@
         <v>12</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I131" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J131" s="17"/>
       <c r="K131" s="9" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M131" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N131" s="7" t="s">
         <v>56</v>
@@ -11263,7 +11094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A132" s="20" t="s">
         <v>14</v>
       </c>
@@ -11293,13 +11124,13 @@
       </c>
       <c r="J132" s="17"/>
       <c r="K132" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M132" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N132" s="7" t="s">
         <v>24</v>
@@ -11330,7 +11161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A133" s="20" t="s">
         <v>14</v>
       </c>
@@ -11362,13 +11193,13 @@
         <v>29</v>
       </c>
       <c r="K133" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L133" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M133" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N133" s="7" t="s">
         <v>56</v>
@@ -11399,7 +11230,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A134" s="20" t="s">
         <v>14</v>
       </c>
@@ -11429,16 +11260,16 @@
       </c>
       <c r="J134" s="17"/>
       <c r="K134" s="8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M134" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N134" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O134" s="7" t="s">
         <v>5</v>
@@ -11452,7 +11283,7 @@
         <v>26</v>
       </c>
       <c r="T134" s="25" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="U134" s="3"/>
       <c r="V134" s="18"/>
@@ -11460,7 +11291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A135" s="20" t="s">
         <v>14</v>
       </c>
@@ -11486,20 +11317,20 @@
         <v>11</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J135" s="17"/>
       <c r="K135" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L135" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M135" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N135" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O135" s="7" t="s">
         <v>5</v>
@@ -11517,7 +11348,7 @@
         <v>26</v>
       </c>
       <c r="T135" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="U135" s="3"/>
       <c r="V135" s="18"/>
@@ -11525,7 +11356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A136" s="20" t="s">
         <v>14</v>
       </c>
@@ -11555,13 +11386,13 @@
       </c>
       <c r="J136" s="17"/>
       <c r="K136" s="8" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M136" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N136" s="7" t="s">
         <v>6</v>
@@ -11586,7 +11417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A137" s="20" t="s">
         <v>14</v>
       </c>
@@ -11615,16 +11446,16 @@
         <v>10</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K137" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L137" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M137" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N137" s="7" t="s">
         <v>24</v>
@@ -11645,13 +11476,13 @@
         <v>13</v>
       </c>
       <c r="V137" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="W137" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A138" s="20" t="s">
         <v>14</v>
       </c>
@@ -11681,13 +11512,13 @@
       </c>
       <c r="J138" s="17"/>
       <c r="K138" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="L138" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M138" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N138" s="7" t="s">
         <v>6</v>
@@ -11712,7 +11543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A139" s="16" t="s">
         <v>14</v>
       </c>
@@ -11723,7 +11554,7 @@
         <v>0.7104166666666667</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E139" s="12">
         <v>-117.374589</v>
@@ -11741,16 +11572,16 @@
         <v>10</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K139" s="9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L139" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M139" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N139" s="7" t="s">
         <v>6</v>
@@ -11764,10 +11595,10 @@
       <c r="Q139" s="5"/>
       <c r="R139" s="4"/>
       <c r="S139" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T139" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="U139" s="3"/>
       <c r="V139" s="18"/>
@@ -11775,7 +11606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A140" s="20" t="s">
         <v>14</v>
       </c>
@@ -11804,16 +11635,16 @@
         <v>10</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K140" s="8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="L140" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M140" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N140" s="7" t="s">
         <v>24</v>
@@ -11835,7 +11666,7 @@
       </c>
       <c r="T140" s="28"/>
       <c r="U140" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V140" s="1" t="s">
         <v>1</v>
@@ -11844,7 +11675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A141" s="20" t="s">
         <v>14</v>
       </c>
@@ -11873,16 +11704,16 @@
         <v>10</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K141" s="8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L141" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M141" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N141" s="7" t="s">
         <v>6</v>
@@ -11896,7 +11727,7 @@
       <c r="Q141" s="5"/>
       <c r="R141" s="4"/>
       <c r="S141" s="29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T141" s="28"/>
       <c r="U141" s="21"/>
@@ -11905,7 +11736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A142" s="20" t="s">
         <v>14</v>
       </c>
@@ -11937,13 +11768,13 @@
         <v>29</v>
       </c>
       <c r="K142" s="8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M142" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N142" s="7" t="s">
         <v>6</v>
@@ -11961,16 +11792,16 @@
       </c>
       <c r="T142" s="28"/>
       <c r="U142" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V142" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="W142" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143" s="20" t="s">
         <v>14</v>
       </c>
@@ -11996,17 +11827,17 @@
         <v>11</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J143" s="17"/>
       <c r="K143" s="9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L143" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M143" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N143" s="7" t="s">
         <v>15</v>
@@ -12037,7 +11868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144" s="20" t="s">
         <v>14</v>
       </c>
@@ -12067,13 +11898,13 @@
       </c>
       <c r="J144" s="17"/>
       <c r="K144" s="8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>21</v>
       </c>
       <c r="M144" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N144" s="7" t="s">
         <v>6</v>
@@ -12098,7 +11929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A145" s="16" t="s">
         <v>14</v>
       </c>
@@ -12108,11 +11939,11 @@
       <c r="C145" s="14">
         <v>0.93888888888888899</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E145" s="12" t="s">
-        <v>87</v>
+      <c r="D145" s="13">
+        <v>34.162182999999999</v>
+      </c>
+      <c r="E145" s="12">
+        <v>-117.564728</v>
       </c>
       <c r="F145" s="11" t="s">
         <v>13</v>
@@ -12127,16 +11958,16 @@
         <v>10</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K145" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L145" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N145" s="7" t="s">
         <v>24</v>
@@ -12161,7 +11992,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A146" s="20" t="s">
         <v>14</v>
       </c>
@@ -12187,17 +12018,17 @@
         <v>11</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J146" s="17"/>
       <c r="K146" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L146" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M146" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N146" s="7" t="s">
         <v>6</v>
@@ -12228,7 +12059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A147" s="43" t="s">
         <v>14</v>
       </c>
@@ -12257,16 +12088,16 @@
         <v>10</v>
       </c>
       <c r="J147" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K147" s="38" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L147" s="38" t="s">
         <v>16</v>
       </c>
       <c r="M147" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N147" s="37" t="s">
         <v>56</v>
@@ -12295,7 +12126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A148" s="20" t="s">
         <v>14</v>
       </c>
@@ -12324,16 +12155,16 @@
         <v>10</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K148" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L148" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M148" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N148" s="7" t="s">
         <v>24</v>
@@ -12362,7 +12193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A149" s="20" t="s">
         <v>14</v>
       </c>
@@ -12392,13 +12223,13 @@
       </c>
       <c r="J149" s="17"/>
       <c r="K149" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L149" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M149" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N149" s="7" t="s">
         <v>56</v>
@@ -12427,7 +12258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A150" s="20" t="s">
         <v>14</v>
       </c>
@@ -12459,13 +12290,13 @@
         <v>29</v>
       </c>
       <c r="K150" s="8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L150" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M150" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N150" s="7" t="s">
         <v>56</v>
@@ -12494,7 +12325,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A151" s="16" t="s">
         <v>14</v>
       </c>
@@ -12504,11 +12335,11 @@
       <c r="C151" s="14">
         <v>0.67986111111111114</v>
       </c>
-      <c r="D151" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>76</v>
+      <c r="D151" s="13">
+        <v>34.034592000000004</v>
+      </c>
+      <c r="E151" s="12">
+        <v>-117.95672500000001</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>13</v>
@@ -12526,13 +12357,13 @@
         <v>29</v>
       </c>
       <c r="K151" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L151" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M151" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N151" s="7" t="s">
         <v>6</v>
@@ -12563,7 +12394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A152" s="16" t="s">
         <v>14</v>
       </c>
@@ -12573,11 +12404,11 @@
       <c r="C152" s="14">
         <v>0.6791666666666667</v>
       </c>
-      <c r="D152" s="13">
-        <v>0</v>
-      </c>
-      <c r="E152" s="12">
-        <v>0</v>
+      <c r="D152" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="F152" s="11" t="s">
         <v>24</v>
@@ -12592,16 +12423,16 @@
         <v>10</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K152" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L152" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M152" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N152" s="7" t="s">
         <v>6</v>
@@ -12630,7 +12461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A153" s="20" t="s">
         <v>14</v>
       </c>
@@ -12659,16 +12490,16 @@
         <v>10</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K153" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L153" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M153" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N153" s="7" t="s">
         <v>6</v>
@@ -12697,7 +12528,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A154" s="20" t="s">
         <v>14</v>
       </c>
@@ -12729,13 +12560,13 @@
         <v>29</v>
       </c>
       <c r="K154" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L154" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M154" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N154" s="7" t="s">
         <v>24</v>
@@ -12760,7 +12591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A155" s="20" t="s">
         <v>14</v>
       </c>
@@ -12789,16 +12620,16 @@
         <v>10</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K155" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L155" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M155" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N155" s="7" t="s">
         <v>56</v>
@@ -12827,7 +12658,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A156" s="20" t="s">
         <v>14</v>
       </c>
@@ -12857,13 +12688,13 @@
       </c>
       <c r="J156" s="17"/>
       <c r="K156" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L156" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M156" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N156" s="7" t="s">
         <v>24</v>
@@ -12890,7 +12721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A157" s="20" t="s">
         <v>14</v>
       </c>
@@ -12919,16 +12750,16 @@
         <v>10</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K157" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L157" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M157" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N157" s="7" t="s">
         <v>6</v>
@@ -12950,7 +12781,7 @@
       </c>
       <c r="T157" s="3"/>
       <c r="U157" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V157" s="1" t="s">
         <v>1</v>
@@ -12959,7 +12790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A158" s="20" t="s">
         <v>14</v>
       </c>
@@ -12988,16 +12819,16 @@
         <v>10</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K158" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L158" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M158" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N158" s="7" t="s">
         <v>6</v>
@@ -13026,7 +12857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A159" s="16" t="s">
         <v>14</v>
       </c>
@@ -13036,11 +12867,11 @@
       <c r="C159" s="14">
         <v>0.36458333333333331</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E159" s="12" t="s">
-        <v>60</v>
+      <c r="D159" s="13">
+        <v>36.329183</v>
+      </c>
+      <c r="E159" s="12">
+        <v>-119.351557</v>
       </c>
       <c r="F159" s="11" t="s">
         <v>13</v>
@@ -13064,7 +12895,7 @@
         <v>16</v>
       </c>
       <c r="M159" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N159" s="7" t="s">
         <v>56</v>
@@ -13093,7 +12924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160" s="20" t="s">
         <v>14</v>
       </c>
@@ -13129,7 +12960,7 @@
         <v>16</v>
       </c>
       <c r="M160" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N160" s="7" t="s">
         <v>6</v>
@@ -13158,7 +12989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" s="20" t="s">
         <v>14</v>
       </c>
@@ -13196,7 +13027,7 @@
         <v>21</v>
       </c>
       <c r="M161" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N161" s="7" t="s">
         <v>6</v>
@@ -13227,7 +13058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" s="20" t="s">
         <v>14</v>
       </c>
@@ -13265,7 +13096,7 @@
         <v>7</v>
       </c>
       <c r="M162" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N162" s="7" t="s">
         <v>24</v>
@@ -13292,7 +13123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" s="20" t="s">
         <v>14</v>
       </c>
@@ -13326,7 +13157,7 @@
         <v>7</v>
       </c>
       <c r="M163" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N163" s="7" t="s">
         <v>6</v>
@@ -13355,7 +13186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" s="20" t="s">
         <v>14</v>
       </c>
@@ -13393,7 +13224,7 @@
         <v>7</v>
       </c>
       <c r="M164" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N164" s="7" t="s">
         <v>6</v>
@@ -13424,7 +13255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" s="20" t="s">
         <v>14</v>
       </c>
@@ -13462,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="M165" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N165" s="7" t="s">
         <v>24</v>
@@ -13489,7 +13320,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" s="20" t="s">
         <v>14</v>
       </c>
@@ -13527,7 +13358,7 @@
         <v>16</v>
       </c>
       <c r="M166" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N166" s="7" t="s">
         <v>6</v>
@@ -13552,7 +13383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" s="20" t="s">
         <v>14</v>
       </c>
@@ -13590,7 +13421,7 @@
         <v>16</v>
       </c>
       <c r="M167" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N167" s="7" t="s">
         <v>6</v>
@@ -13621,7 +13452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" s="16" t="s">
         <v>14</v>
       </c>
@@ -13657,7 +13488,7 @@
         <v>21</v>
       </c>
       <c r="M168" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N168" s="7" t="s">
         <v>6</v>
@@ -13682,7 +13513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" s="20" t="s">
         <v>14</v>
       </c>
@@ -13720,7 +13551,7 @@
         <v>21</v>
       </c>
       <c r="M169" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N169" s="7" t="s">
         <v>6</v>
@@ -13747,7 +13578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" s="20" t="s">
         <v>14</v>
       </c>
@@ -13785,7 +13616,7 @@
         <v>30</v>
       </c>
       <c r="M170" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N170" s="7" t="s">
         <v>6</v>
@@ -13816,7 +13647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" s="20" t="s">
         <v>14</v>
       </c>
@@ -13854,7 +13685,7 @@
         <v>30</v>
       </c>
       <c r="M171" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N171" s="7" t="s">
         <v>6</v>
@@ -13885,7 +13716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" s="20" t="s">
         <v>14</v>
       </c>
@@ -13923,7 +13754,7 @@
         <v>7</v>
       </c>
       <c r="M172" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N172" s="7" t="s">
         <v>25</v>
@@ -13952,7 +13783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" s="16" t="s">
         <v>14</v>
       </c>
@@ -13990,7 +13821,7 @@
         <v>21</v>
       </c>
       <c r="M173" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N173" s="7" t="s">
         <v>6</v>
@@ -14013,7 +13844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" s="16" t="s">
         <v>14</v>
       </c>
@@ -14049,7 +13880,7 @@
         <v>16</v>
       </c>
       <c r="M174" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N174" s="7" t="s">
         <v>15</v>
@@ -14076,7 +13907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" s="16" t="s">
         <v>14</v>
       </c>
@@ -14114,7 +13945,7 @@
         <v>7</v>
       </c>
       <c r="M175" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N175" s="7" t="s">
         <v>6</v>
@@ -14152,144 +13983,39 @@
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:R1"/>
   </mergeCells>
-  <conditionalFormatting sqref="V12:V62">
-    <cfRule type="expression" dxfId="27" priority="28" stopIfTrue="1">
-      <formula>IF(S12&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="Q3:Q175">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>IF(P3="No",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U9:U62">
-    <cfRule type="expression" dxfId="26" priority="27" stopIfTrue="1">
-      <formula>IF(S9&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="R3:R175">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>IF(P3="No",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q9:Q62">
-    <cfRule type="expression" dxfId="25" priority="26">
-      <formula>IF(P9="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R9:R62">
-    <cfRule type="expression" dxfId="24" priority="25">
-      <formula>IF(P9="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V3:V6">
-    <cfRule type="expression" dxfId="23" priority="24" stopIfTrue="1">
+  <conditionalFormatting sqref="U3:U62">
+    <cfRule type="expression" dxfId="4" priority="19" stopIfTrue="1">
       <formula>IF(S3&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:U6">
-    <cfRule type="expression" dxfId="22" priority="23" stopIfTrue="1">
+  <conditionalFormatting sqref="U66">
+    <cfRule type="expression" dxfId="3" priority="13" stopIfTrue="1">
+      <formula>IF(S66&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V3:V68">
+    <cfRule type="expression" dxfId="2" priority="9" stopIfTrue="1">
       <formula>IF(S3&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:Q6">
-    <cfRule type="expression" dxfId="21" priority="22">
-      <formula>IF(P3="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R6">
-    <cfRule type="expression" dxfId="20" priority="21">
-      <formula>IF(P3="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V8">
-    <cfRule type="expression" dxfId="19" priority="20" stopIfTrue="1">
-      <formula>IF(S7&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U8">
-    <cfRule type="expression" dxfId="18" priority="19" stopIfTrue="1">
-      <formula>IF(S7&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:Q8">
-    <cfRule type="expression" dxfId="17" priority="18">
-      <formula>IF(P7="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R8">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>IF(P7="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V9:V11">
-    <cfRule type="expression" dxfId="15" priority="16" stopIfTrue="1">
-      <formula>IF(S9&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q63:Q67">
-    <cfRule type="expression" dxfId="14" priority="15">
-      <formula>IF(P63="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R63:R67">
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>IF(P63="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U66">
-    <cfRule type="expression" dxfId="12" priority="13" stopIfTrue="1">
-      <formula>IF(S66&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V63:V67">
-    <cfRule type="expression" dxfId="11" priority="12" stopIfTrue="1">
-      <formula>IF(S63&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q68:Q133 Q141:Q169 Q171:Q175">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>IF(P68="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R68:R133 R141:R169 R171:R175">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>IF(P68="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V68">
-    <cfRule type="expression" dxfId="8" priority="9" stopIfTrue="1">
-      <formula>IF(S68&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V87 V81:V84 V79 V77 V71:V72">
-    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
+  <conditionalFormatting sqref="V71:V72 V77 V79 V81:V84 V87">
+    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
       <formula>IF(S71&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V89">
-    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>IF(S89&lt;&gt;"Contact From Object",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q134">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>IF(P134="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R134">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>IF(P134="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q135:Q140">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>IF(P135="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R135:R140">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>IF(P135="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q170">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>IF(P170="No",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R170">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>IF(P170="No",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
